--- a/A2259C_B_MARKER.xlsx
+++ b/A2259C_B_MARKER.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://myrp-my.sharepoint.com/personal/paul_z_chen_rp_edu_sg/Documents/A2259C/A2295C graded assignment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="173" documentId="11_A443E1B2FF577DD385915AB3E14BFBF2C597995E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB934BEE-A657-433E-A732-6E060A8BB24A}"/>
+  <xr:revisionPtr revIDLastSave="181" documentId="11_A443E1B2FF577DD385915AB3E14BFBF2C597995E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2AE22DB-9BB7-4B65-AA1D-3CF104A78462}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Meta" sheetId="8" r:id="rId1"/>
     <sheet name="Data1" sheetId="2" r:id="rId2"/>
-    <sheet name="Data2" sheetId="3" r:id="rId3"/>
-    <sheet name="Data3" sheetId="4" r:id="rId4"/>
-    <sheet name="QA_Data1" sheetId="5" r:id="rId5"/>
-    <sheet name="QA_Data2" sheetId="6" r:id="rId6"/>
+    <sheet name="QA_Data1" sheetId="5" r:id="rId3"/>
+    <sheet name="Data2" sheetId="3" r:id="rId4"/>
+    <sheet name="QA_Data2" sheetId="6" r:id="rId5"/>
+    <sheet name="Data3" sheetId="4" r:id="rId6"/>
     <sheet name="QA_Data3" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="270">
   <si>
     <t>Outlet_ID</t>
   </si>
@@ -880,6 +880,15 @@
 3. biodiverse planting.
 At each site, a biodiversity index score was recorded based on species richness and abundance surveys.
 The study aims to examine whether verge management regime is associated with variation in biodiversity index scores.</t>
+  </si>
+  <si>
+    <t>Briefly discuss one limitation of relying on generative AI to solve this question.</t>
+  </si>
+  <si>
+    <t>AI may suggest an incorrect model if context is misunderstood 
+AI may not correctly handle dummy variable creation in Excel 
+AI may give generic interpretations without checking assumptions 
+AI outputs depend on correct user input and may overlook data issues</t>
   </si>
 </sst>
 </file>
@@ -958,7 +967,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -976,6 +985,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3913,6 +3926,176 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C1" t="s">
+        <v>171</v>
+      </c>
+      <c r="D1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>175</v>
+      </c>
+      <c r="C3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>176</v>
+      </c>
+      <c r="C4" t="s">
+        <v>174</v>
+      </c>
+      <c r="D4" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>177</v>
+      </c>
+      <c r="C5" t="s">
+        <v>174</v>
+      </c>
+      <c r="D5" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C6" t="s">
+        <v>174</v>
+      </c>
+      <c r="D6" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>179</v>
+      </c>
+      <c r="C7" t="s">
+        <v>180</v>
+      </c>
+      <c r="D7">
+        <f>AVERAGE(tzdata[Nitrate_mgL])</f>
+        <v>10.255102040816327</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>181</v>
+      </c>
+      <c r="C8" t="s">
+        <v>182</v>
+      </c>
+      <c r="D8">
+        <f>COUNT(tzdata[Nitrate_mgL])</f>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>183</v>
+      </c>
+      <c r="C9" t="s">
+        <v>184</v>
+      </c>
+      <c r="D9">
+        <f>(AVERAGE(tzdata[Nitrate_mgL])-10)/(2.5/SQRT(COUNT(tzdata[Nitrate_mgL])))</f>
+        <v>0.71428571428571597</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>185</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="D10">
+        <f>2*(1-_xlfn.NORM.S.DIST(ABS((AVERAGE(tzdata[Nitrate_mgL])-10)/(2.5/SQRT(COUNT(tzdata[Nitrate_mgL])))),TRUE))</f>
+        <v>0.47505052405395198</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>186</v>
+      </c>
+      <c r="C11" t="s">
+        <v>192</v>
+      </c>
+      <c r="D11" t="str">
+        <f>IF(QA_Data1!D10&lt;0.05,"Reject null","Cannot reject null")</f>
+        <v>Cannot reject null</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C27"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4223,7 +4406,177 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="57.44140625" customWidth="1"/>
+    <col min="3" max="3" width="21.5546875" customWidth="1"/>
+    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C1" t="s">
+        <v>171</v>
+      </c>
+      <c r="D1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D3" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>176</v>
+      </c>
+      <c r="C4" t="s">
+        <v>174</v>
+      </c>
+      <c r="D4" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>195</v>
+      </c>
+      <c r="C5" t="s">
+        <v>174</v>
+      </c>
+      <c r="D5" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>196</v>
+      </c>
+      <c r="C6" t="s">
+        <v>174</v>
+      </c>
+      <c r="D6" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>197</v>
+      </c>
+      <c r="C7" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>199</v>
+      </c>
+      <c r="C8" t="s">
+        <v>200</v>
+      </c>
+      <c r="D8" cm="1">
+        <f t="array" ref="D8">(AVERAGE(tpairdata[After_kWhDay]-tpairdata[Before_kWhDay]))/(_xlfn.SINGLE(_xlfn.STDEV.S(tpairdata[After_kWhDay]-tpairdata[Before_kWhDay]))/SQRT(COUNT(tpairdata[After_kWhDay]-tpairdata[Before_kWhDay])))</f>
+        <v>-5.154769889597894</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>185</v>
+      </c>
+      <c r="C9" t="s">
+        <v>201</v>
+      </c>
+      <c r="D9" cm="1">
+        <f t="array" ref="D9">_xlfn.T.DIST(ABS((AVERAGE(tpairdata[After_kWhDay]-tpairdata[Before_kWhDay]))/(_xlfn.STDEV.S(tpairdata[After_kWhDay]-tpairdata[Before_kWhDay])/SQRT(COUNT(tpairdata[After_kWhDay]-tpairdata[Before_kWhDay])))), COUNT(tpairdata[After_kWhDay]-tpairdata[Before_kWhDay])-1,)</f>
+        <v>3.2243691536910651E-5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>202</v>
+      </c>
+      <c r="C10" t="s">
+        <v>174</v>
+      </c>
+      <c r="D10" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>186</v>
+      </c>
+      <c r="C11" t="s">
+        <v>209</v>
+      </c>
+      <c r="D11" t="str">
+        <f>IF(D9&lt;0.05,"Reject null","Cannot reject null")</f>
+        <v>Reject null</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:O110"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7392,347 +7745,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>169</v>
-      </c>
-      <c r="B1" t="s">
-        <v>170</v>
-      </c>
-      <c r="C1" t="s">
-        <v>171</v>
-      </c>
-      <c r="D1" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>173</v>
-      </c>
-      <c r="C2" t="s">
-        <v>174</v>
-      </c>
-      <c r="D2" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>175</v>
-      </c>
-      <c r="C3" t="s">
-        <v>174</v>
-      </c>
-      <c r="D3" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>176</v>
-      </c>
-      <c r="C4" t="s">
-        <v>174</v>
-      </c>
-      <c r="D4" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>177</v>
-      </c>
-      <c r="C5" t="s">
-        <v>174</v>
-      </c>
-      <c r="D5" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>178</v>
-      </c>
-      <c r="C6" t="s">
-        <v>174</v>
-      </c>
-      <c r="D6" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>179</v>
-      </c>
-      <c r="C7" t="s">
-        <v>180</v>
-      </c>
-      <c r="D7">
-        <f>AVERAGE(tzdata[Nitrate_mgL])</f>
-        <v>10.255102040816327</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>181</v>
-      </c>
-      <c r="C8" t="s">
-        <v>182</v>
-      </c>
-      <c r="D8">
-        <f>COUNT(tzdata[Nitrate_mgL])</f>
-        <v>49</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>183</v>
-      </c>
-      <c r="C9" t="s">
-        <v>184</v>
-      </c>
-      <c r="D9">
-        <f>(AVERAGE(tzdata[Nitrate_mgL])-10)/(2.5/SQRT(COUNT(tzdata[Nitrate_mgL])))</f>
-        <v>0.71428571428571597</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>185</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="D10">
-        <f>2*(1-_xlfn.NORM.S.DIST(ABS((AVERAGE(tzdata[Nitrate_mgL])-10)/(2.5/SQRT(COUNT(tzdata[Nitrate_mgL])))),TRUE))</f>
-        <v>0.47505052405395198</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
-        <v>186</v>
-      </c>
-      <c r="C11" t="s">
-        <v>192</v>
-      </c>
-      <c r="D11" t="str">
-        <f>IF(QA_Data1!D10&lt;0.05,"Reject null","Cannot reject null")</f>
-        <v>Cannot reject null</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>169</v>
-      </c>
-      <c r="B1" t="s">
-        <v>170</v>
-      </c>
-      <c r="C1" t="s">
-        <v>171</v>
-      </c>
-      <c r="D1" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>193</v>
-      </c>
-      <c r="C2" t="s">
-        <v>174</v>
-      </c>
-      <c r="D2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>194</v>
-      </c>
-      <c r="C3" t="s">
-        <v>174</v>
-      </c>
-      <c r="D3" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>176</v>
-      </c>
-      <c r="C4" t="s">
-        <v>174</v>
-      </c>
-      <c r="D4" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C5" t="s">
-        <v>174</v>
-      </c>
-      <c r="D5" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>196</v>
-      </c>
-      <c r="C6" t="s">
-        <v>174</v>
-      </c>
-      <c r="D6" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>197</v>
-      </c>
-      <c r="C7" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>199</v>
-      </c>
-      <c r="C8" t="s">
-        <v>200</v>
-      </c>
-      <c r="D8" cm="1">
-        <f t="array" ref="D8">(AVERAGE(tpairdata[After_kWhDay]-tpairdata[Before_kWhDay]))/(_xlfn.SINGLE(_xlfn.STDEV.S(tpairdata[After_kWhDay]-tpairdata[Before_kWhDay]))/SQRT(COUNT(tpairdata[After_kWhDay]-tpairdata[Before_kWhDay])))</f>
-        <v>-5.154769889597894</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>185</v>
-      </c>
-      <c r="C9" t="s">
-        <v>201</v>
-      </c>
-      <c r="D9" cm="1">
-        <f t="array" ref="D9">_xlfn.T.DIST(ABS((AVERAGE(tpairdata[After_kWhDay]-tpairdata[Before_kWhDay]))/(_xlfn.STDEV.S(tpairdata[After_kWhDay]-tpairdata[Before_kWhDay])/SQRT(COUNT(tpairdata[After_kWhDay]-tpairdata[Before_kWhDay])))), COUNT(tpairdata[After_kWhDay]-tpairdata[Before_kWhDay])-1,)</f>
-        <v>3.2243691536910651E-5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>202</v>
-      </c>
-      <c r="C10" t="s">
-        <v>174</v>
-      </c>
-      <c r="D10" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
-        <v>186</v>
-      </c>
-      <c r="C11" t="s">
-        <v>209</v>
-      </c>
-      <c r="D11" t="str">
-        <f>IF(D9&lt;0.05,"Reject null","Cannot reject null")</f>
-        <v>Reject null</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.44140625" bestFit="1" customWidth="1"/>
@@ -7742,169 +7757,188 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="8" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2">
+      <c r="A2" s="8">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="8" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3">
+      <c r="A3" s="8">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="8" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4">
+      <c r="A4" s="8">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="8" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5">
+      <c r="A5" s="8">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="8" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6">
+      <c r="A6" s="8">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="8" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7">
+      <c r="A7" s="8">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="8" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8">
+      <c r="A8" s="8">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="8" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9">
+      <c r="A9" s="8">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="8" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10">
+      <c r="A10" s="8">
         <v>9</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="D10">
+      <c r="C10" s="8"/>
+      <c r="D10" s="8">
         <v>2.1485273492286123</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11">
+      <c r="A11" s="8">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="8">
         <v>0.17015497608178701</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12">
+      <c r="A12" s="8">
         <v>11</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="D12" t="str">
+      <c r="D12" s="8" t="str">
         <f>IF(Data3!L13&lt;0.05,"Reject null","Cannot reject null")</f>
         <v>Reject null</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="8">
+        <v>12</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="C13" s="8"/>
+      <c r="D13" s="9" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D14" cm="1">
+        <f t="array" aca="1" ref="D14" ca="1">A14:D14</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
